--- a/output/pdf_financials_xlsx/AME.xlsx
+++ b/output/pdf_financials_xlsx/AME.xlsx
@@ -1297,25 +1297,25 @@
         <v>-0.525324</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="17">
@@ -1597,25 +1597,25 @@
         <v>-0.525324</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="21">
@@ -1771,25 +1771,25 @@
         <v>-0.525324</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="24">
@@ -1957,10 +1957,10 @@
         <v>119.104222</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-77.967814</v>
+        <v>77.967814</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-109.6603</v>
+        <v>109.6603</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-134.367767</v>
+        <v>134.367767</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-153.327633</v>
+        <v>153.327633</v>
       </c>
     </row>
     <row r="27">
@@ -2011,25 +2011,25 @@
         <v>-0.525324</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="28">
@@ -2127,25 +2127,25 @@
         <v>-0.525324</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="30">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>416.7812844509562</v>
+        <v>-416.7812844509562</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>144.2872341499145</v>
+        <v>-144.2872341499145</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2273,25 +2273,25 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>416.7812844509562</v>
+        <v>-416.7812844509562</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>144.2872341499145</v>
+        <v>-144.2872341499145</v>
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
@@ -6034,37 +6034,37 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.188833</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.188833</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.188833</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.063552</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.909757</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.646688</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.086166</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.282709</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.322751</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.388059</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.439905</v>
       </c>
     </row>
     <row r="93">
@@ -10311,7 +10311,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -13867,7 +13871,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15170,7 +15178,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15768,7 +15780,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16570,7 +16586,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -17079,7 +17099,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17586,7 +17610,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -37076,25 +37104,25 @@
         </is>
       </c>
       <c r="O283" s="5" t="n">
-        <v>3.493244</v>
+        <v>-3.493244</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>2.716477</v>
+        <v>-2.716477</v>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>5.457747</v>
+        <v>-5.457747</v>
       </c>
       <c r="R283" s="5" t="n">
-        <v>3.289809</v>
+        <v>-3.289809</v>
       </c>
       <c r="S283" s="5" t="n">
-        <v>1.667755</v>
+        <v>-1.667755</v>
       </c>
       <c r="T283" s="5" t="n">
-        <v>4.031033</v>
+        <v>-4.031033</v>
       </c>
       <c r="U283" s="5" t="n">
-        <v>4.599829</v>
+        <v>-4.599829</v>
       </c>
     </row>
     <row r="284">

--- a/output/pdf_financials_xlsx/AME.xlsx
+++ b/output/pdf_financials_xlsx/AME.xlsx
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002096</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000293</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -2011,10 +2011,10 @@
         <v>-0.525324</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.493244</v>
+        <v>-3.49534</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.716477</v>
+        <v>-2.71677</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-5.457747</v>
@@ -2127,10 +2127,10 @@
         <v>-0.525324</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.493244</v>
+        <v>-3.49534</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.716477</v>
+        <v>-2.71677</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-5.457747</v>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-416.7812844509562</v>
+        <v>-417.0313596166787</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-144.2872341499145</v>
+        <v>-144.3027970129926</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2413,19 +2413,19 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.033607</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.107679</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007955</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.014057</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.02799</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.202003</v>
@@ -2533,19 +2533,19 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.033607</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.107679</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007955</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.014057</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.02799</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.202003</v>
@@ -3253,19 +3253,19 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.033607</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.150472</v>
+        <v>0.042793</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011863</v>
+        <v>0.003908</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.017524</v>
+        <v>0.003467</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.25299</v>
+        <v>0.225</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -43076,7 +43076,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -43284,7 +43284,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -45411,7 +45411,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
